--- a/artfynd/A 22223-2026 artfynd.xlsx
+++ b/artfynd/A 22223-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ88"/>
+  <dimension ref="A1:AZ92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11783,6 +11783,470 @@
       <c r="AZ88" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129619279</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>136624894</v>
+      </c>
+      <c r="B89" t="n">
+        <v>43457</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Uppsala Län, Upl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>621232</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6648684</v>
+      </c>
+      <c r="S89" t="n">
+        <v>8</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136624894</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>136624895</v>
+      </c>
+      <c r="B90" t="n">
+        <v>43457</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Uppsala Län, Upl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>621153</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6649056</v>
+      </c>
+      <c r="S90" t="n">
+        <v>8</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF90" t="inlineStr"/>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136624895</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>136624897</v>
+      </c>
+      <c r="B91" t="n">
+        <v>43457</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr"/>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Uppsala Län, Upl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>621138</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6649160</v>
+      </c>
+      <c r="S91" t="n">
+        <v>8</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136624897</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>136624899</v>
+      </c>
+      <c r="B92" t="n">
+        <v>43457</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>100942</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Väddnätfjäril</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Euphydryas aurinia</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="J92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L92" t="inlineStr"/>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Uppsala Län, Upl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>621135</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6649160</v>
+      </c>
+      <c r="S92" t="n">
+        <v>8</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Järlåsa</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Milad Avalinejad Bandari</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Hannah Norman</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr">
+        <is>
+          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+        </is>
+      </c>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136624899</t>
         </is>
       </c>
     </row>
@@ -11875,6 +12339,10 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 22223-2026 artfynd.xlsx
+++ b/artfynd/A 22223-2026 artfynd.xlsx
@@ -11791,7 +11791,7 @@
         <v>136624894</v>
       </c>
       <c r="B89" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>136624895</v>
       </c>
       <c r="B90" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>136624897</v>
       </c>
       <c r="B91" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136624899</v>
       </c>
       <c r="B92" t="n">
-        <v>43457</v>
+        <v>43459</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 22223-2026 artfynd.xlsx
+++ b/artfynd/A 22223-2026 artfynd.xlsx
@@ -11893,7 +11893,7 @@
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
@@ -12009,7 +12009,7 @@
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
@@ -12125,7 +12125,7 @@
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">

--- a/artfynd/A 22223-2026 artfynd.xlsx
+++ b/artfynd/A 22223-2026 artfynd.xlsx
@@ -11816,7 +11816,11 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr">
         <is>
@@ -11893,7 +11897,7 @@
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
@@ -11932,7 +11936,11 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr">
         <is>
@@ -12009,7 +12017,7 @@
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
@@ -12048,7 +12056,11 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr">
         <is>
@@ -12125,7 +12137,7 @@
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
@@ -12164,7 +12176,11 @@
           <t>(Rottemburg, 1775)</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr">
         <is>
@@ -12241,7 +12257,7 @@
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>Biogeografisk uppföljning av fjärilar, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
+          <t>Biogeografisk uppföljning av fjärilar, ÅGP väddnätfjäril, C-län, C260313 Uppsala biogeografisk uppföljning väddnätfjäril 2026</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">

--- a/artfynd/A 22223-2026 artfynd.xlsx
+++ b/artfynd/A 22223-2026 artfynd.xlsx
@@ -11791,7 +11791,7 @@
         <v>136624894</v>
       </c>
       <c r="B89" t="n">
-        <v>43459</v>
+        <v>43472</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>136624895</v>
       </c>
       <c r="B90" t="n">
-        <v>43459</v>
+        <v>43472</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>136624897</v>
       </c>
       <c r="B91" t="n">
-        <v>43459</v>
+        <v>43472</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>136624899</v>
       </c>
       <c r="B92" t="n">
-        <v>43459</v>
+        <v>43472</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 22223-2026 artfynd.xlsx
+++ b/artfynd/A 22223-2026 artfynd.xlsx
@@ -11791,7 +11791,7 @@
         <v>136624894</v>
       </c>
       <c r="B89" t="n">
-        <v>43472</v>
+        <v>43474</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11911,7 +11911,7 @@
         <v>136624895</v>
       </c>
       <c r="B90" t="n">
-        <v>43472</v>
+        <v>43474</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12031,7 +12031,7 @@
         <v>136624897</v>
       </c>
       <c r="B91" t="n">
-        <v>43472</v>
+        <v>43474</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12151,7 +12151,7 @@
         <v>136624899</v>
       </c>
       <c r="B92" t="n">
-        <v>43472</v>
+        <v>43474</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 22223-2026 artfynd.xlsx
+++ b/artfynd/A 22223-2026 artfynd.xlsx
@@ -11822,11 +11822,7 @@
         </is>
       </c>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
@@ -11942,11 +11938,7 @@
         </is>
       </c>
       <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K90" t="inlineStr"/>
       <c r="L90" t="inlineStr"/>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
@@ -12062,11 +12054,7 @@
         </is>
       </c>
       <c r="J91" t="inlineStr"/>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
@@ -12182,11 +12170,7 @@
         </is>
       </c>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>larv/nymf</t>
-        </is>
-      </c>
+      <c r="K92" t="inlineStr"/>
       <c r="L92" t="inlineStr"/>
       <c r="M92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>

--- a/artfynd/A 22223-2026 artfynd.xlsx
+++ b/artfynd/A 22223-2026 artfynd.xlsx
@@ -11791,7 +11791,7 @@
         <v>136624894</v>
       </c>
       <c r="B89" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>136624895</v>
       </c>
       <c r="B90" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>136624897</v>
       </c>
       <c r="B91" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136624899</v>
       </c>
       <c r="B92" t="n">
-        <v>43474</v>
+        <v>43484</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>

--- a/artfynd/A 22223-2026 artfynd.xlsx
+++ b/artfynd/A 22223-2026 artfynd.xlsx
@@ -11791,7 +11791,7 @@
         <v>136624894</v>
       </c>
       <c r="B89" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -11907,7 +11907,7 @@
         <v>136624895</v>
       </c>
       <c r="B90" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12023,7 +12023,7 @@
         <v>136624897</v>
       </c>
       <c r="B91" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12139,7 +12139,7 @@
         <v>136624899</v>
       </c>
       <c r="B92" t="n">
-        <v>43484</v>
+        <v>43485</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
